--- a/artfynd/A 9221-2024 artfynd.xlsx
+++ b/artfynd/A 9221-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73695649</v>
+        <v>73695648</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>20A, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432350.9323583042</v>
+        <v>432386</v>
       </c>
       <c r="R2" t="n">
-        <v>6407010.040420035</v>
+        <v>6407026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +752,9 @@
           <t>2018-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73695651</v>
+        <v>73695650</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432331.7738648746</v>
+        <v>432196</v>
       </c>
       <c r="R3" t="n">
-        <v>6406855.247811668</v>
+        <v>6406985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +853,9 @@
           <t>2018-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73695648</v>
+        <v>73695651</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,26 +914,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>20A, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432385.9133836661</v>
+        <v>432332</v>
       </c>
       <c r="R4" t="n">
-        <v>6407025.976377614</v>
+        <v>6406855</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,19 +954,9 @@
           <t>2018-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,12 +990,7 @@
         <v>73695652</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432349.2588385292</v>
+        <v>432349</v>
       </c>
       <c r="R5" t="n">
-        <v>6406846.958065117</v>
+        <v>6406847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1064,9 @@
           <t>2018-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,6 +1090,107 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>73695649</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20A, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>432351</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6407010</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bottnaryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-10-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-10-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Sandbarrsvampar</t>
         </is>

--- a/artfynd/A 9221-2024 artfynd.xlsx
+++ b/artfynd/A 9221-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695648</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695650</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695651</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695652</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,8 +1220,20 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695649</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>